--- a/Data/BP.xlsx
+++ b/Data/BP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pouniq/BloodPressure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pouniq/BloodPressure/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886287CF-1E49-344F-98F6-1265B2CE5172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EC06C-566F-0E4C-8602-E940CE6075A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="0" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{ECD6C929-F296-5945-A84D-FAEE2E8C4A93}"/>
   </bookViews>
@@ -1432,6 +1432,12 @@
       <c r="E38">
         <v>121</v>
       </c>
+      <c r="F38">
+        <v>121</v>
+      </c>
+      <c r="G38">
+        <v>118</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
@@ -1443,6 +1449,12 @@
       <c r="E39">
         <v>72</v>
       </c>
+      <c r="F39">
+        <v>66</v>
+      </c>
+      <c r="G39">
+        <v>75</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
@@ -1454,6 +1466,12 @@
       <c r="E40">
         <v>60</v>
       </c>
+      <c r="F40">
+        <v>70</v>
+      </c>
+      <c r="G40">
+        <v>70</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
@@ -1467,6 +1485,12 @@
       <c r="E41">
         <v>111</v>
       </c>
+      <c r="F41">
+        <v>132</v>
+      </c>
+      <c r="G41">
+        <v>127</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
@@ -1478,6 +1502,12 @@
       <c r="E42">
         <v>73</v>
       </c>
+      <c r="F42">
+        <v>74</v>
+      </c>
+      <c r="G42">
+        <v>68</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
@@ -1489,6 +1519,12 @@
       <c r="E43">
         <v>60</v>
       </c>
+      <c r="F43">
+        <v>73</v>
+      </c>
+      <c r="G43">
+        <v>60</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
@@ -1660,28 +1696,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A44:A49"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="B50:B55"/>
     <mergeCell ref="B56:B61"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="C56:C58"/>
@@ -1698,6 +1712,28 @@
     <mergeCell ref="C41:C43"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="B50:B55"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="C32:C34"/>
   </mergeCells>

--- a/Data/BP.xlsx
+++ b/Data/BP.xlsx
@@ -2,41 +2,37 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pouniq/BloodPressure/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EC06C-566F-0E4C-8602-E940CE6075A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A0D29FFC-A735-1841-BD85-8CEB58677D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="0" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{ECD6C929-F296-5945-A84D-FAEE2E8C4A93}"/>
+    <workbookView xWindow="380" yWindow="0" windowWidth="28040" windowHeight="17440" xr2:uid="{54DB268E-0F8D-AB4B-99D9-45144FAC5121}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="BP" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="22">
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>hand</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
   <si>
     <t>morning</t>
   </si>
@@ -47,10 +43,10 @@
     <t>night</t>
   </si>
   <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>type</t>
+    <t>1405/2/8</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
   <si>
     <t>Systolic</t>
@@ -62,19 +58,7 @@
     <t>Pulse</t>
   </si>
   <si>
-    <t>hand</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>L</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>1405/2/8</t>
   </si>
   <si>
     <t>1405/2/9</t>
@@ -108,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -117,21 +101,315 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -139,18 +417,204 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -481,382 +945,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E505C231-E7B7-654F-8FD4-DEC046EAC11C}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>149</v>
-      </c>
-      <c r="E2">
-        <v>140</v>
-      </c>
-      <c r="F2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>89</v>
-      </c>
-      <c r="E3">
-        <v>74</v>
-      </c>
-      <c r="F3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>65</v>
-      </c>
-      <c r="E4">
-        <v>83</v>
-      </c>
-      <c r="F4">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>151</v>
-      </c>
-      <c r="E5">
-        <v>141</v>
-      </c>
-      <c r="F5">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>78</v>
-      </c>
-      <c r="E6">
-        <v>75</v>
-      </c>
-      <c r="F6">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>60</v>
-      </c>
-      <c r="E7">
-        <v>64</v>
-      </c>
-      <c r="F7">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>127</v>
-      </c>
-      <c r="E8">
-        <v>142</v>
-      </c>
-      <c r="F8">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="C21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="C24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="C30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DE1C3F-CED3-DF4F-9573-AC1A0B7CA3E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA597E4-D04D-3C45-9AD3-C1821D5F940C}">
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>149</v>
@@ -869,11 +1014,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>89</v>
@@ -886,11 +1028,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>65</v>
@@ -903,43 +1042,35 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
+      <c r="C8" t="s">
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
+      <c r="C11" t="s">
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>151</v>
@@ -952,11 +1083,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>78</v>
@@ -969,11 +1097,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>60</v>
@@ -986,17 +1111,17 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>9</v>
+      <c r="C14" t="s">
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>142</v>
@@ -1006,11 +1131,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>70</v>
@@ -1020,11 +1142,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16">
         <v>66</v>
@@ -1034,13 +1153,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>127</v>
@@ -1053,11 +1170,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>83</v>
@@ -1070,11 +1184,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19">
         <v>64</v>
@@ -1087,17 +1198,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>4</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>9</v>
+      <c r="C20" t="s">
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>133</v>
@@ -1110,11 +1221,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>60</v>
@@ -1127,11 +1235,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>56</v>
@@ -1144,13 +1249,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1" t="s">
-        <v>10</v>
+      <c r="C23" t="s">
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>128</v>
@@ -1163,11 +1266,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>75</v>
@@ -1180,11 +1280,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>54</v>
@@ -1197,17 +1294,17 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>5</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>9</v>
+      <c r="C26" t="s">
+        <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>130</v>
@@ -1220,11 +1317,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E27">
         <v>75</v>
@@ -1237,11 +1331,8 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>59</v>
@@ -1254,13 +1345,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1" t="s">
-        <v>10</v>
+      <c r="C29" t="s">
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>143</v>
@@ -1273,11 +1362,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>74</v>
@@ -1290,11 +1376,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E31">
         <v>60</v>
@@ -1307,17 +1390,17 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>6</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>9</v>
+      <c r="C32" t="s">
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>121</v>
@@ -1330,11 +1413,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>68</v>
@@ -1347,11 +1427,8 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E34">
         <v>60</v>
@@ -1364,13 +1441,11 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1" t="s">
-        <v>10</v>
+      <c r="C35" t="s">
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>123</v>
@@ -1383,11 +1458,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>68</v>
@@ -1400,11 +1472,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E37">
         <v>64</v>
@@ -1417,17 +1486,17 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>7</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>9</v>
+      <c r="C38" t="s">
+        <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E38">
         <v>121</v>
@@ -1440,11 +1509,8 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39">
         <v>72</v>
@@ -1457,11 +1523,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E40">
         <v>60</v>
@@ -1474,13 +1537,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1" t="s">
-        <v>10</v>
+      <c r="C41" t="s">
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E41">
         <v>111</v>
@@ -1493,11 +1554,8 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E42">
         <v>73</v>
@@ -1510,11 +1568,8 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E43">
         <v>60</v>
@@ -1527,217 +1582,132 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>8</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>9</v>
+      <c r="C44" t="s">
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1" t="s">
-        <v>10</v>
+      <c r="C47" t="s">
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>9</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>9</v>
+      <c r="C50" t="s">
+        <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1" t="s">
-        <v>10</v>
+      <c r="C53" t="s">
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
       <c r="D54" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
-        <v>10</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="A56">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>9</v>
+      <c r="C56" t="s">
+        <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1" t="s">
-        <v>10</v>
+      <c r="C59" t="s">
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="B44:B49"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A44:A49"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="B50:B55"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C32:C34"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/BP.xlsx
+++ b/Data/BP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pouniq/BloodPressure/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A0D29FFC-A735-1841-BD85-8CEB58677D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9FC1F-9701-2541-BED9-6C5C9E6D74DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="0" windowWidth="28040" windowHeight="17440" xr2:uid="{54DB268E-0F8D-AB4B-99D9-45144FAC5121}"/>
   </bookViews>
@@ -1594,15 +1594,42 @@
       <c r="D44" t="s">
         <v>9</v>
       </c>
+      <c r="E44">
+        <v>116</v>
+      </c>
+      <c r="F44">
+        <v>112</v>
+      </c>
+      <c r="G44">
+        <v>126</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D45" t="s">
         <v>10</v>
       </c>
+      <c r="E45">
+        <v>67</v>
+      </c>
+      <c r="F45">
+        <v>66</v>
+      </c>
+      <c r="G45">
+        <v>68</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D46" t="s">
         <v>11</v>
+      </c>
+      <c r="E46">
+        <v>56</v>
+      </c>
+      <c r="F46">
+        <v>78</v>
+      </c>
+      <c r="G46">
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -1612,18 +1639,45 @@
       <c r="D47" t="s">
         <v>9</v>
       </c>
+      <c r="E47">
+        <v>123</v>
+      </c>
+      <c r="F47">
+        <v>129</v>
+      </c>
+      <c r="G47">
+        <v>133</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D48" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>86</v>
+      </c>
+      <c r="F48">
+        <v>65</v>
+      </c>
+      <c r="G48">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D49" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49">
+        <v>71</v>
+      </c>
+      <c r="G49">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>9</v>
       </c>
@@ -1636,36 +1690,90 @@
       <c r="D50" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>127</v>
+      </c>
+      <c r="F50">
+        <v>137</v>
+      </c>
+      <c r="G50">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D51" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51">
+        <v>75</v>
+      </c>
+      <c r="F51">
+        <v>72</v>
+      </c>
+      <c r="G51">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D52" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52">
+        <v>67</v>
+      </c>
+      <c r="F52">
+        <v>85</v>
+      </c>
+      <c r="G52">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53">
+        <v>123</v>
+      </c>
+      <c r="F53">
+        <v>125</v>
+      </c>
+      <c r="G53">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D54" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <v>70</v>
+      </c>
+      <c r="F54">
+        <v>71</v>
+      </c>
+      <c r="G54">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D55" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55">
+        <v>68</v>
+      </c>
+      <c r="F55">
+        <v>80</v>
+      </c>
+      <c r="G55">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -1679,17 +1787,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D58" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
         <v>12</v>
       </c>
@@ -1697,12 +1805,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D60" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D61" t="s">
         <v>11</v>
       </c>

--- a/Data/BP.xlsx
+++ b/Data/BP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pouniq/BloodPressure/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9FC1F-9701-2541-BED9-6C5C9E6D74DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368095F5-3E34-514A-8AB8-4D4CACD329C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="0" windowWidth="28040" windowHeight="17440" xr2:uid="{54DB268E-0F8D-AB4B-99D9-45144FAC5121}"/>
   </bookViews>
@@ -1786,15 +1786,42 @@
       <c r="D56" t="s">
         <v>9</v>
       </c>
+      <c r="E56">
+        <v>132</v>
+      </c>
+      <c r="F56">
+        <v>114</v>
+      </c>
+      <c r="G56">
+        <v>116</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
         <v>10</v>
       </c>
+      <c r="E57">
+        <v>68</v>
+      </c>
+      <c r="F57">
+        <v>59</v>
+      </c>
+      <c r="G57">
+        <v>72</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D58" t="s">
         <v>11</v>
+      </c>
+      <c r="E58">
+        <v>64</v>
+      </c>
+      <c r="F58">
+        <v>68</v>
+      </c>
+      <c r="G58">
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -1804,15 +1831,42 @@
       <c r="D59" t="s">
         <v>9</v>
       </c>
+      <c r="E59">
+        <v>133</v>
+      </c>
+      <c r="F59">
+        <v>122</v>
+      </c>
+      <c r="G59">
+        <v>123</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D60" t="s">
         <v>10</v>
       </c>
+      <c r="E60">
+        <v>73</v>
+      </c>
+      <c r="F60">
+        <v>63</v>
+      </c>
+      <c r="G60">
+        <v>70</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D61" t="s">
         <v>11</v>
+      </c>
+      <c r="E61">
+        <v>66</v>
+      </c>
+      <c r="F61">
+        <v>68</v>
+      </c>
+      <c r="G61">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
